--- a/src/MultiPeriodCalculator.Console/Files/my.xlsx
+++ b/src/MultiPeriodCalculator.Console/Files/my.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\MultiPeriodCalculator.Console\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A0CD6C-AF9E-4DD7-A27E-57A933E62011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76B68BC-E4A9-4412-81ED-E02A1739B9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="85">
   <si>
     <t>ID</t>
   </si>
@@ -123,9 +123,6 @@
     <t>Betrag</t>
   </si>
   <si>
-    <t>Initialer Saldo</t>
-  </si>
-  <si>
     <t>IN</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <t>Steuer-Id</t>
   </si>
   <si>
-    <t># Setup Kontosaldi</t>
-  </si>
-  <si>
     <t># Exogene Konti</t>
   </si>
   <si>
@@ -292,6 +286,18 @@
   </si>
   <si>
     <t>Einkauf PK Nidi</t>
+  </si>
+  <si>
+    <t>Initialer Saldo 3a</t>
+  </si>
+  <si>
+    <t># Setup Konti</t>
+  </si>
+  <si>
+    <t>Initialer Saldo PK Maria</t>
+  </si>
+  <si>
+    <t>Initialer Saldo PK Nidi</t>
   </si>
 </sst>
 </file>
@@ -694,19 +700,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
@@ -720,22 +726,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>25279</v>
       </c>
       <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -759,10 +765,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>5</v>
@@ -843,7 +849,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -853,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
@@ -864,7 +870,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -886,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -897,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -908,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -919,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
@@ -930,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>15</v>
@@ -938,7 +944,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -948,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
@@ -959,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
@@ -967,7 +973,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -977,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>12</v>
@@ -988,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>12</v>
@@ -999,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>12</v>
@@ -1010,7 +1016,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>12</v>
@@ -1021,7 +1027,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>12</v>
@@ -1032,7 +1038,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>12</v>
@@ -1040,7 +1046,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1094,7 +1100,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>16</v>
@@ -1179,11 +1185,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6223A4C6-1802-4880-8580-86AB5C9C2946}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
@@ -1211,12 +1217,12 @@
         <v>24</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1230,22 +1236,16 @@
         <v>45658</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>200000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1253,22 +1253,16 @@
         <v>45658</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>80000</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1276,16 +1270,16 @@
         <v>45658</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>150000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1293,16 +1287,16 @@
         <v>45658</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6">
-        <v>50000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1310,98 +1304,80 @@
         <v>45658</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>79</v>
+      <c r="A8" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>17000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45839</v>
+        <v>45658</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>7258</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46204</v>
+        <v>45658</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>7258</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>46569</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>7258</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
+      <c r="A11" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46935</v>
+        <v>45839</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1413,18 +1389,18 @@
         <v>7258</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>47300</v>
+        <v>46204</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1436,18 +1412,18 @@
         <v>7258</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>47665</v>
+        <v>46569</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -1459,18 +1435,18 @@
         <v>7258</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>48030</v>
+        <v>46935</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>9</v>
@@ -1482,18 +1458,18 @@
         <v>7258</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>48396</v>
+        <v>47300</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>9</v>
@@ -1505,92 +1481,92 @@
         <v>7258</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>80</v>
+      <c r="A17" s="2">
+        <v>47665</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>7258</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45839</v>
+        <v>48030</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>7258</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46204</v>
+        <v>48396</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>7258</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>46569</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-      <c r="D20">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>7258</v>
-      </c>
-      <c r="F20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46935</v>
+        <v>45839</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -1602,18 +1578,18 @@
         <v>7258</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>47300</v>
+        <v>46204</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -1625,18 +1601,18 @@
         <v>7258</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>47665</v>
+        <v>46569</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -1648,18 +1624,18 @@
         <v>7258</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>48030</v>
+        <v>46935</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -1671,18 +1647,18 @@
         <v>7258</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>48396</v>
+        <v>47300</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -1694,92 +1670,92 @@
         <v>7258</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>81</v>
+      <c r="A26" s="2">
+        <v>47665</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>7258</v>
+      </c>
+      <c r="F26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>45839</v>
+        <v>48030</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>50000</v>
+        <v>7258</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46204</v>
+        <v>48396</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>50000</v>
+        <v>7258</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>46569</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29">
-        <v>9</v>
-      </c>
-      <c r="D29">
-        <v>7</v>
-      </c>
-      <c r="E29">
-        <v>50000</v>
-      </c>
-      <c r="F29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" t="s">
-        <v>30</v>
+      <c r="A29" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46935</v>
+        <v>45839</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>9</v>
@@ -1791,18 +1767,18 @@
         <v>50000</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>47300</v>
+        <v>46204</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31">
         <v>9</v>
@@ -1814,18 +1790,18 @@
         <v>50000</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>47665</v>
+        <v>46569</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -1837,18 +1813,18 @@
         <v>50000</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>48030</v>
+        <v>46935</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>9</v>
@@ -1860,18 +1836,18 @@
         <v>50000</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>48396</v>
+        <v>47300</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -1883,92 +1859,92 @@
         <v>50000</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>76</v>
+      <c r="A35" s="2">
+        <v>47665</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>50000</v>
+      </c>
+      <c r="F35" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>45658</v>
+        <v>48030</v>
       </c>
       <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>50000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" t="s">
         <v>29</v>
-      </c>
-      <c r="C36">
-        <v>17</v>
-      </c>
-      <c r="D36">
-        <v>9</v>
-      </c>
-      <c r="E36">
-        <v>90000</v>
-      </c>
-      <c r="F36" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>45839</v>
+        <v>48396</v>
       </c>
       <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+      <c r="E37">
+        <v>50000</v>
+      </c>
+      <c r="F37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" t="s">
         <v>29</v>
       </c>
-      <c r="C37">
-        <v>17</v>
-      </c>
-      <c r="D37">
-        <v>9</v>
-      </c>
-      <c r="E37">
-        <v>90000</v>
-      </c>
-      <c r="F37" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>46023</v>
-      </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38">
-        <v>17</v>
-      </c>
-      <c r="D38">
-        <v>9</v>
-      </c>
-      <c r="E38">
-        <v>90000</v>
-      </c>
-      <c r="F38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G38" t="s">
-        <v>27</v>
+      <c r="A38" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>46204</v>
+        <v>45658</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39">
         <v>17</v>
@@ -1980,18 +1956,18 @@
         <v>90000</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46388</v>
+        <v>45839</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40">
         <v>17</v>
@@ -2003,18 +1979,18 @@
         <v>90000</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46569</v>
+        <v>46023</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41">
         <v>17</v>
@@ -2026,18 +2002,18 @@
         <v>90000</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46753</v>
+        <v>46204</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42">
         <v>17</v>
@@ -2049,18 +2025,18 @@
         <v>90000</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46935</v>
+        <v>46388</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43">
         <v>17</v>
@@ -2072,18 +2048,18 @@
         <v>90000</v>
       </c>
       <c r="F43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>47119</v>
+        <v>46569</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44">
         <v>17</v>
@@ -2095,18 +2071,18 @@
         <v>90000</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>47300</v>
+        <v>46753</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45">
         <v>17</v>
@@ -2118,18 +2094,18 @@
         <v>90000</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>47484</v>
+        <v>46935</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>17</v>
@@ -2141,18 +2117,18 @@
         <v>90000</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>47665</v>
+        <v>47119</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>17</v>
@@ -2164,18 +2140,18 @@
         <v>90000</v>
       </c>
       <c r="F47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>47849</v>
+        <v>47300</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48">
         <v>17</v>
@@ -2187,18 +2163,18 @@
         <v>90000</v>
       </c>
       <c r="F48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>48030</v>
+        <v>47484</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49">
         <v>17</v>
@@ -2210,18 +2186,18 @@
         <v>90000</v>
       </c>
       <c r="F49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>48214</v>
+        <v>47665</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -2233,18 +2209,18 @@
         <v>90000</v>
       </c>
       <c r="F50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>48396</v>
+        <v>47849</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51">
         <v>17</v>
@@ -2256,92 +2232,92 @@
         <v>90000</v>
       </c>
       <c r="F51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>48030</v>
+      </c>
+      <c r="B52" t="s">
         <v>28</v>
       </c>
-      <c r="G51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>77</v>
+      <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>9</v>
+      </c>
+      <c r="E52">
+        <v>90000</v>
+      </c>
+      <c r="F52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45658</v>
+        <v>48214</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53">
         <v>17</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E53">
-        <v>15000</v>
+        <v>90000</v>
       </c>
       <c r="F53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>45839</v>
+        <v>48396</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54">
         <v>17</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54">
-        <v>15000</v>
+        <v>90000</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>46023</v>
-      </c>
-      <c r="B55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C55">
-        <v>17</v>
-      </c>
-      <c r="D55">
-        <v>10</v>
-      </c>
-      <c r="E55">
-        <v>15000</v>
-      </c>
-      <c r="F55" t="s">
-        <v>28</v>
-      </c>
-      <c r="G55" t="s">
-        <v>27</v>
+      <c r="A55" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46204</v>
+        <v>45658</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C56">
         <v>17</v>
@@ -2353,18 +2329,18 @@
         <v>15000</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>46388</v>
+        <v>45839</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57">
         <v>17</v>
@@ -2376,18 +2352,18 @@
         <v>15000</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>46569</v>
+        <v>46023</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58">
         <v>17</v>
@@ -2399,18 +2375,18 @@
         <v>15000</v>
       </c>
       <c r="F58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46753</v>
+        <v>46204</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C59">
         <v>17</v>
@@ -2422,18 +2398,18 @@
         <v>15000</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46935</v>
+        <v>46388</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C60">
         <v>17</v>
@@ -2445,18 +2421,18 @@
         <v>15000</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>47119</v>
+        <v>46569</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C61">
         <v>17</v>
@@ -2468,18 +2444,18 @@
         <v>15000</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>47300</v>
+        <v>46753</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C62">
         <v>17</v>
@@ -2491,18 +2467,18 @@
         <v>15000</v>
       </c>
       <c r="F62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>47484</v>
+        <v>46935</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C63">
         <v>17</v>
@@ -2514,18 +2490,18 @@
         <v>15000</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>47665</v>
+        <v>47119</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C64">
         <v>17</v>
@@ -2537,18 +2513,18 @@
         <v>15000</v>
       </c>
       <c r="F64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>47849</v>
+        <v>47300</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65">
         <v>17</v>
@@ -2560,18 +2536,18 @@
         <v>15000</v>
       </c>
       <c r="F65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>48030</v>
+        <v>47484</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C66">
         <v>17</v>
@@ -2583,18 +2559,18 @@
         <v>15000</v>
       </c>
       <c r="F66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>48214</v>
+        <v>47665</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C67">
         <v>17</v>
@@ -2606,18 +2582,18 @@
         <v>15000</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>48396</v>
+        <v>47849</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>17</v>
@@ -2629,92 +2605,92 @@
         <v>15000</v>
       </c>
       <c r="F68" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>48030</v>
+      </c>
+      <c r="B69" t="s">
         <v>28</v>
       </c>
-      <c r="G68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>56</v>
+      <c r="C69">
+        <v>17</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69">
+        <v>15000</v>
+      </c>
+      <c r="F69" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>46022</v>
+        <v>48214</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D70">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E70">
-        <v>85000</v>
+        <v>15000</v>
       </c>
       <c r="F70" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>46387</v>
+        <v>48396</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C71">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D71">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E71">
-        <v>85000</v>
+        <v>15000</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>46752</v>
-      </c>
-      <c r="B72" t="s">
-        <v>43</v>
-      </c>
-      <c r="C72">
-        <v>11</v>
-      </c>
-      <c r="D72">
-        <v>21</v>
-      </c>
-      <c r="E72">
-        <v>85000</v>
-      </c>
-      <c r="F72" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" t="s">
-        <v>30</v>
+      <c r="A72" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>47118</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C73">
         <v>11</v>
@@ -2729,15 +2705,15 @@
         <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>47483</v>
+        <v>46387</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C74">
         <v>11</v>
@@ -2752,15 +2728,15 @@
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>47848</v>
+        <v>46752</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C75">
         <v>11</v>
@@ -2775,15 +2751,15 @@
         <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>48213</v>
+        <v>47118</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C76">
         <v>11</v>
@@ -2798,15 +2774,15 @@
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>48579</v>
+        <v>47483</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C77">
         <v>11</v>
@@ -2821,7 +2797,76 @@
         <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>47848</v>
+      </c>
+      <c r="B78" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78">
+        <v>11</v>
+      </c>
+      <c r="D78">
+        <v>21</v>
+      </c>
+      <c r="E78">
+        <v>85000</v>
+      </c>
+      <c r="F78" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>48213</v>
+      </c>
+      <c r="B79" t="s">
+        <v>42</v>
+      </c>
+      <c r="C79">
+        <v>11</v>
+      </c>
+      <c r="D79">
+        <v>21</v>
+      </c>
+      <c r="E79">
+        <v>85000</v>
+      </c>
+      <c r="F79" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>48579</v>
+      </c>
+      <c r="B80" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80">
+        <v>11</v>
+      </c>
+      <c r="D80">
+        <v>21</v>
+      </c>
+      <c r="E80">
+        <v>85000</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2831,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E396F9D1-6955-4D48-853A-4775D5AE5B10}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -2855,13 +2900,13 @@
         <v>23</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,10 +2914,10 @@
         <v>48579</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -2881,10 +2926,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,10 +2937,10 @@
         <v>48579</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -2904,10 +2949,102 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>48579</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>48579</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>48579</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>48579</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2941,13 +3078,13 @@
         <v>23</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2955,7 +3092,7 @@
         <v>45292</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -2970,7 +3107,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2978,7 +3115,7 @@
         <v>45658</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -2993,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3001,7 +3138,7 @@
         <v>46023</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -3016,7 +3153,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3038,13 +3175,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -3067,10 +3204,10 @@
         <v>46387</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3079,7 +3216,7 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3088,10 +3225,10 @@
         <v>45657</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3109,10 +3246,10 @@
         <v>46022</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3129,10 +3266,10 @@
         <v>46387</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3152,10 +3289,10 @@
         <v>45657</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3164,7 +3301,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3175,10 +3312,10 @@
         <v>46022</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3187,7 +3324,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3198,10 +3335,10 @@
         <v>46387</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3210,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
